--- a/podaci/excel/bicikli_2026-10.xlsx
+++ b/podaci/excel/bicikli_2026-10.xlsx
@@ -1,59 +1,59 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="15a" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="15b" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="20a" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="20b" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="22a" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="22b" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="23a" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="25a" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="26" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="27a" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="27b" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="28" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="29a" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="29b" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="30a" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="30b" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="31b" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="34a" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="34b" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="36a" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="36b" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="37a" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="38a" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="38b" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="39a" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="39b" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="40a" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="40b" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="41" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="42a" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="42b" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="43a" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="43b" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="44a" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="44b" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="45a" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="45b" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="46a" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="46b" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="47" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet name="49a" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet name="49b" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet name="50a" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet name="50b" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet name="51a" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet name="51b" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet name="Info" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15a" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15b" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20a" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20b" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22a" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22b" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23a" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25a" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27a" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27b" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29a" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29b" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30a" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30b" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="31b" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="34a" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="34b" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="36a" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="36b" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="37a" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="38a" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="38b" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="39a" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="39b" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="40a" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="40b" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="41" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="42a" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="42b" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="43a" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="43b" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="44a" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="44b" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="45a" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="45b" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="46a" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="46b" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="47" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="49a" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="49b" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="50a" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="50b" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="51a" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="51b" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="47" state="visible" r:id="rId47"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -975,10 +975,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -990,10 +989,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -1201,10 +1199,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -2047,10 +2044,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="34">
@@ -2062,10 +2058,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="35">
@@ -2273,10 +2268,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3119,10 +3113,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="34">
@@ -3134,10 +3127,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="35">
@@ -3345,10 +3337,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="50">
@@ -4291,10 +4282,15 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>18</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="34">
@@ -4306,10 +4302,15 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>33</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="35">
@@ -4601,10 +4602,15 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>14</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="50">
@@ -5591,10 +5597,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="34">
@@ -5606,10 +5611,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="35">
@@ -5817,10 +5821,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="50">
@@ -6663,10 +6666,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="34">
@@ -6678,10 +6680,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="35">
@@ -6889,10 +6890,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -7735,10 +7735,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="34">
@@ -7750,10 +7749,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="35">
@@ -7961,10 +7959,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -8807,10 +8804,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="34">
@@ -8822,10 +8818,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -9033,10 +9028,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="50">
@@ -9879,10 +9873,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="34">
@@ -9894,10 +9887,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="35">
@@ -10105,10 +10097,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="50">
@@ -10951,10 +10942,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="34">
@@ -10966,10 +10956,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>93</v>
       </c>
     </row>
     <row r="35">
@@ -11177,10 +11166,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="50">
@@ -12023,10 +12011,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="34">
@@ -12038,10 +12025,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="35">
@@ -12249,10 +12235,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="50">
@@ -13095,10 +13080,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -13110,10 +13094,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="35">
@@ -13321,10 +13304,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -14167,10 +14149,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="34">
@@ -14182,10 +14163,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="35">
@@ -14393,10 +14373,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="50">
@@ -15239,10 +15218,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="34">
@@ -15254,10 +15232,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="35">
@@ -15465,10 +15442,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -16311,10 +16287,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="34">
@@ -16326,10 +16301,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="35">
@@ -16537,10 +16511,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -17383,10 +17356,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="34">
@@ -17398,10 +17370,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="35">
@@ -17609,10 +17580,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="50">
@@ -18455,10 +18425,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="34">
@@ -18470,10 +18439,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -18681,10 +18649,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="50">
@@ -19527,10 +19494,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -19542,10 +19508,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="35">
@@ -19753,10 +19718,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -20599,10 +20563,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="34">
@@ -20614,10 +20577,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="35">
@@ -20825,10 +20787,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="50">
@@ -21771,10 +21732,15 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>13</v>
+      </c>
+      <c r="E33" t="n">
+        <v>11</v>
+      </c>
+      <c r="F33" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="34">
@@ -21786,10 +21752,15 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>23</v>
+      </c>
+      <c r="E34" t="n">
+        <v>9</v>
+      </c>
+      <c r="F34" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -22081,10 +22052,15 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="50">
@@ -23171,10 +23147,15 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="34">
@@ -23186,10 +23167,15 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" t="n">
+        <v>11</v>
+      </c>
+      <c r="F34" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="35">
@@ -23481,10 +23467,15 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="50">
@@ -24571,10 +24562,15 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>28</v>
+      </c>
+      <c r="E33" t="n">
+        <v>14</v>
+      </c>
+      <c r="F33" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="34">
@@ -24586,10 +24582,15 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>31</v>
+      </c>
+      <c r="E34" t="n">
+        <v>20</v>
+      </c>
+      <c r="F34" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="35">
@@ -24881,10 +24882,15 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -25871,10 +25877,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -25886,10 +25891,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="35">
@@ -26097,10 +26101,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -26943,10 +26946,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -26958,10 +26960,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -27169,10 +27170,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -28015,10 +28015,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -28030,10 +28029,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="35">
@@ -28241,10 +28239,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="50">
@@ -29087,10 +29084,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="34">
@@ -29102,10 +29098,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="35">
@@ -29313,10 +29308,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -30159,10 +30153,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="34">
@@ -30174,10 +30167,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="35">
@@ -30385,10 +30377,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -31231,10 +31222,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="34">
@@ -31246,10 +31236,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="35">
@@ -31457,10 +31446,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -32303,10 +32291,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="34">
@@ -32318,10 +32305,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="35">
@@ -32529,10 +32515,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="50">
@@ -33375,10 +33360,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="34">
@@ -33390,10 +33374,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="35">
@@ -33601,10 +33584,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -34447,10 +34429,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="34">
@@ -34462,10 +34443,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="35">
@@ -34673,10 +34653,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -35619,10 +35598,15 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9</v>
+      </c>
+      <c r="F33" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="34">
@@ -35634,10 +35618,15 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>16</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16</v>
+      </c>
+      <c r="F34" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -35929,10 +35918,15 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>6</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="50">
@@ -37019,10 +37013,15 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>13</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16</v>
+      </c>
+      <c r="F33" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="34">
@@ -37034,10 +37033,15 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>31</v>
+      </c>
+      <c r="E34" t="n">
+        <v>10</v>
+      </c>
+      <c r="F34" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="35">
@@ -37329,10 +37333,15 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" t="n">
+        <v>5</v>
+      </c>
+      <c r="F49" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="50">
@@ -38319,10 +38328,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="34">
@@ -38334,10 +38342,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="35">
@@ -38545,10 +38552,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -39491,10 +39497,15 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>6</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="34">
@@ -39506,10 +39517,15 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>15</v>
+      </c>
+      <c r="E34" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="35">
@@ -39801,10 +39817,15 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -40791,10 +40812,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -40806,10 +40826,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -41017,10 +41036,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -41863,10 +41881,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -41878,10 +41895,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -42089,10 +42105,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -42935,10 +42950,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="34">
@@ -42950,10 +42964,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -43161,10 +43174,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -44007,10 +44019,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -44022,10 +44033,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="35">
@@ -44233,10 +44243,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -45179,10 +45188,15 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="34">
@@ -45194,10 +45208,15 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>7</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="35">
@@ -45489,10 +45508,15 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>6</v>
+      </c>
+      <c r="E49" t="n">
+        <v>5</v>
+      </c>
+      <c r="F49" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="50">
@@ -46579,10 +46603,15 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>27</v>
+      </c>
+      <c r="E33" t="n">
+        <v>36</v>
+      </c>
+      <c r="F33" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="34">
@@ -46594,10 +46623,15 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>29</v>
+      </c>
+      <c r="E34" t="n">
+        <v>52</v>
+      </c>
+      <c r="F34" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="35">
@@ -46889,10 +46923,15 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>8</v>
+      </c>
+      <c r="E49" t="n">
+        <v>6</v>
+      </c>
+      <c r="F49" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="50">
@@ -48017,10 +48056,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="34">
@@ -48032,10 +48070,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -48243,10 +48280,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="50">
@@ -49089,10 +49125,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -49104,10 +49139,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -49315,10 +49349,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -50161,10 +50194,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="34">
@@ -50176,10 +50208,9 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="35">
@@ -50387,10 +50418,9 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="50">
@@ -51333,10 +51363,15 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>7</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="34">
@@ -51348,10 +51383,15 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>7</v>
+      </c>
+      <c r="E34" t="n">
+        <v>22</v>
+      </c>
+      <c r="F34" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="35">
@@ -51643,10 +51683,15 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -52733,10 +52778,15 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -52748,10 +52798,15 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>9</v>
+      </c>
+      <c r="E34" t="n">
+        <v>11</v>
+      </c>
+      <c r="F34" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="35">
@@ -53043,10 +53098,15 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>zastarelo</t>
-        </is>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="50">

--- a/podaci/excel/bicikli_2026-10.xlsx
+++ b/podaci/excel/bicikli_2026-10.xlsx
@@ -78,7 +78,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -87,7 +87,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -103,12 +113,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -530,6 +542,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -545,6 +558,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -560,6 +574,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -575,6 +590,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -590,6 +606,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -605,6 +622,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -620,6 +638,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -635,6 +654,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -650,6 +670,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -665,6 +686,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -680,6 +702,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -695,6 +718,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -710,6 +734,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -725,6 +750,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -740,6 +766,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -769,6 +796,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1599,6 +1627,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -1614,6 +1643,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1629,6 +1659,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1644,6 +1675,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1659,6 +1691,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1674,6 +1707,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1689,6 +1723,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1704,6 +1739,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1719,6 +1755,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1734,6 +1771,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1749,6 +1787,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1764,6 +1803,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1779,6 +1819,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1794,6 +1835,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1809,6 +1851,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1838,6 +1881,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -2668,6 +2712,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -2683,6 +2728,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -2698,6 +2744,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -2713,6 +2760,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -2728,6 +2776,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -2743,6 +2792,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -2758,6 +2808,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -2773,6 +2824,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -2788,6 +2840,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -2803,6 +2856,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -2818,6 +2872,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -2833,6 +2888,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -2848,6 +2904,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -2863,6 +2920,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -2878,6 +2936,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -2907,6 +2966,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -3747,6 +3807,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -3762,6 +3825,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -3777,6 +3843,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -3792,6 +3861,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -3807,6 +3879,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -3822,6 +3897,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -3837,6 +3915,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -3852,6 +3933,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -3867,6 +3951,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -3882,6 +3969,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -3897,6 +3987,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -3912,6 +4005,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -3927,6 +4023,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -3942,6 +4041,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -3957,6 +4059,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -3992,6 +4097,9 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -4142,14 +4250,18 @@
           <t>01:00</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D26" t="n">
         <v>23</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="4" t="n">
         <v>23</v>
       </c>
     </row>
@@ -4162,14 +4274,18 @@
           <t>02:00</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D27" t="n">
         <v>11</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" s="4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4182,14 +4298,18 @@
           <t>03:00</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D28" t="n">
         <v>7</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" s="4" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4202,14 +4322,18 @@
           <t>04:00</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D29" t="n">
         <v>7</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="4" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4222,14 +4346,18 @@
           <t>05:00</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D30" t="n">
         <v>4</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" s="4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4242,14 +4370,18 @@
           <t>06:00</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D31" t="n">
         <v>5</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="4" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4262,14 +4394,18 @@
           <t>07:00</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D32" t="n">
         <v>9</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" s="4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4282,14 +4418,18 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D33" t="n">
         <v>18</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="4" t="n">
         <v>18</v>
       </c>
     </row>
@@ -4302,14 +4442,18 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D34" t="n">
         <v>33</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="4" t="n">
         <v>33</v>
       </c>
     </row>
@@ -4322,14 +4466,18 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D35" t="n">
         <v>68</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35" s="4" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4342,14 +4490,18 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D36" t="n">
         <v>87</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36" s="4" t="n">
         <v>87</v>
       </c>
     </row>
@@ -4362,14 +4514,18 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D37" t="n">
         <v>79</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37" s="4" t="n">
         <v>79</v>
       </c>
     </row>
@@ -4382,14 +4538,18 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D38" t="n">
         <v>106</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" s="4" t="n">
         <v>106</v>
       </c>
     </row>
@@ -4402,14 +4562,18 @@
           <t>14:00</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D39" t="n">
         <v>95</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" s="4" t="n">
         <v>95</v>
       </c>
     </row>
@@ -4422,14 +4586,18 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D40" t="n">
         <v>121</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40" s="4" t="n">
         <v>121</v>
       </c>
     </row>
@@ -4442,14 +4610,18 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D41" t="n">
         <v>127</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" s="4" t="n">
         <v>127</v>
       </c>
     </row>
@@ -4462,14 +4634,18 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D42" t="n">
         <v>82</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42" s="4" t="n">
         <v>82</v>
       </c>
     </row>
@@ -4482,14 +4658,18 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D43" t="n">
         <v>82</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" s="4" t="n">
         <v>82</v>
       </c>
     </row>
@@ -4502,14 +4682,18 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D44" t="n">
         <v>58</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="4" t="n">
         <v>58</v>
       </c>
     </row>
@@ -4522,14 +4706,18 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D45" t="n">
         <v>60</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" s="4" t="n">
         <v>60</v>
       </c>
     </row>
@@ -4542,14 +4730,18 @@
           <t>21:00</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D46" t="n">
         <v>56</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46" s="4" t="n">
         <v>56</v>
       </c>
     </row>
@@ -4562,14 +4754,18 @@
           <t>22:00</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D47" t="n">
         <v>38</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47" s="4" t="n">
         <v>38</v>
       </c>
     </row>
@@ -4582,14 +4778,18 @@
           <t>23:00</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D48" t="n">
         <v>24</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48" s="4" t="n">
         <v>24</v>
       </c>
     </row>
@@ -4602,14 +4802,18 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D49" t="n">
         <v>14</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49" s="4" t="n">
         <v>14</v>
       </c>
     </row>
@@ -4622,14 +4826,18 @@
           <t>01:00</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D50" t="n">
         <v>6</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4642,14 +4850,18 @@
           <t>02:00</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D51" t="n">
         <v>10</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51" s="4" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4662,14 +4874,18 @@
           <t>03:00</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D52" t="n">
         <v>7</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52" s="4" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4682,14 +4898,18 @@
           <t>04:00</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D53" t="n">
         <v>4</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53" s="4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4702,14 +4922,18 @@
           <t>05:00</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D54" t="n">
         <v>4</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54" s="4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4722,14 +4946,18 @@
           <t>06:00</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D55" t="n">
         <v>4</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55" s="4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4742,14 +4970,18 @@
           <t>07:00</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D56" t="n">
         <v>3</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4762,14 +4994,18 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D57" t="n">
         <v>1</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4782,14 +5018,18 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D58" t="n">
         <v>6</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4802,14 +5042,18 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D59" t="n">
         <v>5</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59" s="4" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4822,14 +5066,18 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D60" t="n">
         <v>12</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60" s="4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4842,14 +5090,18 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D61" t="n">
         <v>8</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61" s="4" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4862,14 +5114,18 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D62" t="n">
         <v>6</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4882,14 +5138,18 @@
           <t>14:00</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D63" t="n">
         <v>14</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63" s="4" t="n">
         <v>14</v>
       </c>
     </row>
@@ -4902,14 +5162,18 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D64" t="n">
         <v>12</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F64" s="4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4922,14 +5186,18 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D65" t="n">
         <v>21</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65" s="4" t="n">
         <v>21</v>
       </c>
     </row>
@@ -4942,14 +5210,18 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D66" t="n">
         <v>15</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66" s="4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -4962,14 +5234,18 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D67" t="n">
         <v>23</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67" s="4" t="n">
         <v>23</v>
       </c>
     </row>
@@ -4982,14 +5258,18 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D68" t="n">
         <v>37</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68" s="4" t="n">
         <v>37</v>
       </c>
     </row>
@@ -5002,14 +5282,18 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D69" t="n">
         <v>34</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69" s="4" t="n">
         <v>34</v>
       </c>
     </row>
@@ -5022,14 +5306,18 @@
           <t>21:00</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D70" t="n">
         <v>27</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70" s="4" t="n">
         <v>27</v>
       </c>
     </row>
@@ -5042,14 +5330,18 @@
           <t>22:00</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D71" t="n">
         <v>29</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71" s="4" t="n">
         <v>29</v>
       </c>
     </row>
@@ -5062,14 +5354,18 @@
           <t>23:00</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D72" t="n">
         <v>30</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72" s="4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -5082,14 +5378,18 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>nula_dan (Sum2)</t>
+        </is>
+      </c>
       <c r="D73" t="n">
         <v>20</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -5152,6 +5452,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -5167,6 +5468,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -5182,6 +5484,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -5197,6 +5500,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -5212,6 +5516,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -5227,6 +5532,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -5242,6 +5548,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -5257,6 +5564,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -5272,6 +5580,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -5287,6 +5596,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -5302,6 +5612,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -5317,6 +5628,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -5332,6 +5644,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -5347,6 +5660,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -5362,6 +5676,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -5391,6 +5706,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -6221,6 +6537,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -6236,6 +6553,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -6251,6 +6569,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -6266,6 +6585,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -6281,6 +6601,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -6296,6 +6617,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -6311,6 +6633,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -6326,6 +6649,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -6341,6 +6665,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -6356,6 +6681,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -6371,6 +6697,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -6386,6 +6713,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -6401,6 +6729,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -6416,6 +6745,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -6431,6 +6761,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -6460,6 +6791,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -7290,6 +7622,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -7305,6 +7638,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -7320,6 +7654,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -7335,6 +7670,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -7350,6 +7686,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -7365,6 +7702,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -7380,6 +7718,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -7395,6 +7734,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -7410,6 +7750,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -7425,6 +7766,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -7440,6 +7782,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -7455,6 +7798,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -7470,6 +7814,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -7485,6 +7830,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -7500,6 +7846,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -7529,6 +7876,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -8359,6 +8707,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -8374,6 +8723,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -8389,6 +8739,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -8404,6 +8755,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -8419,6 +8771,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -8434,6 +8787,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -8449,6 +8803,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -8464,6 +8819,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -8479,6 +8835,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -8494,6 +8851,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -8509,6 +8867,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -8524,6 +8883,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -8539,6 +8899,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -8554,6 +8915,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -8569,6 +8931,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -8598,6 +8961,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -9428,6 +9792,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -9443,6 +9808,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -9458,6 +9824,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -9473,6 +9840,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -9488,6 +9856,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -9503,6 +9872,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -9518,6 +9888,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -9533,6 +9904,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -9548,6 +9920,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -9563,6 +9936,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -9578,6 +9952,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -9593,6 +9968,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -9608,6 +9984,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -9623,6 +10000,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -9638,6 +10016,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -9667,6 +10046,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -10497,6 +10877,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -10512,6 +10893,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -10527,6 +10909,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -10542,6 +10925,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -10557,6 +10941,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -10572,6 +10957,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -10587,6 +10973,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -10602,6 +10989,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -10617,6 +11005,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -10632,6 +11021,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -10647,6 +11037,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -10662,6 +11053,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -10677,6 +11069,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -10692,6 +11085,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -10707,6 +11101,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -10736,6 +11131,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -11566,6 +11962,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -11581,6 +11978,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -11596,6 +11994,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -11611,6 +12010,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -11626,6 +12026,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -11641,6 +12042,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -11656,6 +12058,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -11671,6 +12074,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -11686,6 +12090,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -11701,6 +12106,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -11716,6 +12122,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -11731,6 +12138,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -11746,6 +12154,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -11761,6 +12170,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -11776,6 +12186,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -11805,6 +12216,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -12635,6 +13047,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -12650,6 +13063,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -12665,6 +13079,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -12680,6 +13095,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -12695,6 +13111,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -12710,6 +13127,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -12725,6 +13143,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -12740,6 +13159,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -12755,6 +13175,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -12770,6 +13191,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -12785,6 +13207,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -12800,6 +13223,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -12815,6 +13239,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -12830,6 +13255,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -12845,6 +13271,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -12874,6 +13301,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -13704,6 +14132,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -13719,6 +14148,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -13734,6 +14164,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -13749,6 +14180,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -13764,6 +14196,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -13779,6 +14212,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -13794,6 +14228,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -13809,6 +14244,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -13824,6 +14260,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -13839,6 +14276,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -13854,6 +14292,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -13869,6 +14308,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -13884,6 +14324,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -13899,6 +14340,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -13914,6 +14356,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -13943,6 +14386,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -14773,6 +15217,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -14788,6 +15233,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -14803,6 +15249,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -14818,6 +15265,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -14833,6 +15281,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -14848,6 +15297,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -14863,6 +15313,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -14878,6 +15329,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -14893,6 +15345,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -14908,6 +15361,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -14923,6 +15377,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -14938,6 +15393,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -14953,6 +15409,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -14968,6 +15425,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -14983,6 +15441,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -15012,6 +15471,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -15358,8 +15818,12 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="n">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>nula_niz</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15372,8 +15836,12 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="n">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>nula_niz</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15386,8 +15854,12 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="n">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>nula_niz</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15842,6 +16314,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -15857,6 +16330,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -15872,6 +16346,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -15887,6 +16362,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -15902,6 +16378,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -15917,6 +16394,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -15932,6 +16410,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -15947,6 +16426,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -15962,6 +16442,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -15977,6 +16458,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -15992,6 +16474,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -16007,6 +16490,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -16022,6 +16506,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -16037,6 +16522,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -16052,6 +16538,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -16081,6 +16568,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -16911,6 +17399,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -16926,6 +17415,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -16941,6 +17431,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -16956,6 +17447,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -16971,6 +17463,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -16986,6 +17479,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -17001,6 +17495,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -17016,6 +17511,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -17031,6 +17527,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -17046,6 +17543,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -17061,6 +17559,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -17076,6 +17575,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -17091,6 +17591,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -17106,6 +17607,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -17121,6 +17623,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -17150,6 +17653,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -17980,6 +18484,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -17995,6 +18500,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -18010,6 +18516,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -18025,6 +18532,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -18040,6 +18548,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -18055,6 +18564,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -18070,6 +18580,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -18085,6 +18596,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -18100,6 +18612,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -18115,6 +18628,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -18130,6 +18644,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -18145,6 +18660,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -18160,6 +18676,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -18175,6 +18692,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -18190,6 +18708,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -18219,6 +18738,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -19049,6 +19569,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -19064,6 +19585,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -19079,6 +19601,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -19094,6 +19617,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -19109,6 +19633,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -19124,6 +19649,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -19139,6 +19665,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -19154,6 +19681,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -19169,6 +19697,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -19184,6 +19713,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -19199,6 +19729,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -19214,6 +19745,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -19229,6 +19761,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -19244,6 +19777,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -19259,6 +19793,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -19288,6 +19823,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -20118,6 +20654,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -20133,6 +20670,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -20148,6 +20686,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -20163,6 +20702,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -20178,6 +20718,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -20193,6 +20734,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -20208,6 +20750,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -20223,6 +20766,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -20238,6 +20782,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -20253,6 +20798,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -20268,6 +20814,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -20283,6 +20830,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -20298,6 +20846,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -20313,6 +20862,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -20328,6 +20878,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -20357,6 +20908,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -21197,6 +21749,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -21212,6 +21767,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -21227,6 +21785,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -21242,6 +21803,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -21257,6 +21821,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -21272,6 +21839,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -21287,6 +21857,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -21302,6 +21875,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -21317,6 +21893,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -21332,6 +21911,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -21347,6 +21929,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -21362,6 +21947,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -21377,6 +21965,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -21392,6 +21983,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -21407,6 +22001,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -21442,6 +22039,9 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -22612,6 +23212,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -22627,6 +23230,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -22642,6 +23248,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -22657,6 +23266,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -22672,6 +23284,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -22687,6 +23302,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -22702,6 +23320,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -22717,6 +23338,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -22732,6 +23356,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -22747,6 +23374,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -22762,6 +23392,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -22777,6 +23410,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -22792,6 +23428,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -22807,6 +23446,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -22822,6 +23464,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -22857,6 +23502,9 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -24027,6 +24675,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -24042,6 +24693,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -24057,6 +24711,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -24072,6 +24729,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -24087,6 +24747,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -24102,6 +24765,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -24117,6 +24783,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -24132,6 +24801,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -24147,6 +24819,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -24162,6 +24837,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -24177,6 +24855,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -24192,6 +24873,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -24207,6 +24891,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -24222,6 +24909,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -24237,6 +24927,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -24272,6 +24965,9 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -25432,6 +26128,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -25447,6 +26144,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -25462,6 +26160,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -25477,6 +26176,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -25492,6 +26192,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -25507,6 +26208,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -25522,6 +26224,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -25537,6 +26240,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -25552,6 +26256,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -25567,6 +26272,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -25582,6 +26288,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -25597,6 +26304,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -25612,6 +26320,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -25627,6 +26336,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -25642,6 +26352,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -25671,6 +26382,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -26501,6 +27213,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -26516,6 +27229,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -26531,6 +27245,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -26546,6 +27261,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -26561,6 +27277,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -26576,6 +27293,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -26591,6 +27309,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -26606,6 +27325,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -26621,6 +27341,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -26636,6 +27357,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -26651,6 +27373,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -26666,6 +27389,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -26681,6 +27405,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -26696,6 +27421,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -26711,6 +27437,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -26740,6 +27467,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -26932,8 +27660,12 @@
           <t>07:00</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="n">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>nula_niz</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26946,8 +27678,12 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="n">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>nula_niz</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26960,8 +27696,12 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="n">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>nula_niz</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26974,8 +27714,12 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="n">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>nula_niz</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27100,8 +27844,12 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="n">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>nula_niz</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27114,8 +27862,12 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="n">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>nula_niz</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27128,8 +27880,12 @@
           <t>21:00</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="n">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>nula_niz</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27184,8 +27940,12 @@
           <t>01:00</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="n">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27198,8 +27958,12 @@
           <t>02:00</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="n">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27212,8 +27976,12 @@
           <t>03:00</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="n">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27226,8 +27994,12 @@
           <t>04:00</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="n">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27240,8 +28012,12 @@
           <t>05:00</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="n">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27254,8 +28030,12 @@
           <t>06:00</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="n">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27268,8 +28048,12 @@
           <t>07:00</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="n">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27282,8 +28066,12 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="n">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27296,8 +28084,12 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="n">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27310,8 +28102,12 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="n">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27324,8 +28120,12 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="n">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27338,8 +28138,12 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="n">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27352,8 +28156,12 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="n">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27366,8 +28174,12 @@
           <t>14:00</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="n">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27380,8 +28192,12 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="n">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27394,8 +28210,12 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="n">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27408,8 +28228,12 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="n">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27422,8 +28246,12 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="n">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27436,8 +28264,12 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="n">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27450,8 +28282,12 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="n">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27464,8 +28300,12 @@
           <t>21:00</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="n">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27478,8 +28318,12 @@
           <t>22:00</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="n">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27492,8 +28336,12 @@
           <t>23:00</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="n">
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27506,8 +28354,12 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="n">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27570,6 +28422,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -27585,6 +28438,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -27600,6 +28454,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -27615,6 +28470,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -27630,6 +28486,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -27645,6 +28502,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -27660,6 +28518,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -27675,6 +28534,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -27690,6 +28550,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -27705,6 +28566,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -27720,6 +28582,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -27735,6 +28598,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -27750,6 +28614,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -27765,6 +28630,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -27780,6 +28646,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -27809,6 +28676,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -28639,6 +29507,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -28654,6 +29523,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -28669,6 +29539,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -28684,6 +29555,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -28699,6 +29571,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -28714,6 +29587,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -28729,6 +29603,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -28744,6 +29619,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -28759,6 +29635,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -28774,6 +29651,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -28789,6 +29667,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -28804,6 +29683,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -28819,6 +29699,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -28834,6 +29715,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -28849,6 +29731,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -28878,6 +29761,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -29708,6 +30592,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -29723,6 +30608,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -29738,6 +30624,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -29753,6 +30640,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -29768,6 +30656,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -29783,6 +30672,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -29798,6 +30688,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -29813,6 +30704,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -29828,6 +30720,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -29843,6 +30736,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -29858,6 +30752,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -29873,6 +30768,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -29888,6 +30784,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -29903,6 +30800,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -29918,6 +30816,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -29947,6 +30846,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -30777,6 +31677,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -30792,6 +31693,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -30807,6 +31709,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -30822,6 +31725,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -30837,6 +31741,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -30852,6 +31757,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -30867,6 +31773,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -30882,6 +31789,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -30897,6 +31805,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -30912,6 +31821,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -30927,6 +31837,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -30942,6 +31853,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -30957,6 +31869,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -30972,6 +31885,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -30987,6 +31901,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -31016,6 +31931,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -31846,6 +32762,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -31861,6 +32778,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -31876,6 +32794,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -31891,6 +32810,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -31906,6 +32826,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -31921,6 +32842,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -31936,6 +32858,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -31951,6 +32874,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -31966,6 +32890,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -31981,6 +32906,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -31996,6 +32922,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -32011,6 +32938,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -32026,6 +32954,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -32041,6 +32970,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -32056,6 +32986,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -32085,6 +33016,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -32915,6 +33847,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -32930,6 +33863,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -32945,6 +33879,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -32960,6 +33895,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -32975,6 +33911,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -32990,6 +33927,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -33005,6 +33943,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -33020,6 +33959,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -33035,6 +33975,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -33050,6 +33991,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -33065,6 +34007,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -33080,6 +34023,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -33095,6 +34039,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -33110,6 +34055,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -33125,6 +34071,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -33154,6 +34101,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -33984,6 +34932,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -33999,6 +34948,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -34014,6 +34964,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -34029,6 +34980,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -34044,6 +34996,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -34059,6 +35012,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -34074,6 +35028,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -34089,6 +35044,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -34104,6 +35060,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -34119,6 +35076,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -34134,6 +35092,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -34149,6 +35108,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -34164,6 +35124,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -34179,6 +35140,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -34194,6 +35156,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -34223,6 +35186,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -35063,6 +36027,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -35078,6 +36045,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -35093,6 +36063,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -35108,6 +36081,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -35123,6 +36099,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -35138,6 +36117,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -35153,6 +36135,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -35168,6 +36153,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -35183,6 +36171,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -35198,6 +36189,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -35213,6 +36207,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -35228,6 +36225,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -35243,6 +36243,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -35258,6 +36261,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -35273,6 +36279,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -35308,6 +36317,9 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -36478,6 +37490,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -36493,6 +37508,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -36508,6 +37526,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -36523,6 +37544,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -36538,6 +37562,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -36553,6 +37580,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -36568,6 +37598,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -36583,6 +37616,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -36598,6 +37634,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -36613,6 +37652,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -36628,6 +37670,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -36643,6 +37688,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -36658,6 +37706,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -36673,6 +37724,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -36688,6 +37742,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -36723,6 +37780,9 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -37883,6 +38943,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -37898,6 +38959,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -37913,6 +38975,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -37928,6 +38991,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -37943,6 +39007,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -37958,6 +39023,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -37973,6 +39039,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -37988,6 +39055,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -38003,6 +39071,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -38018,6 +39087,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -38033,6 +39103,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -38048,6 +39119,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -38063,6 +39135,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -38078,6 +39151,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -38093,6 +39167,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -38122,6 +39197,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -38962,6 +40038,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -38977,6 +40056,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -38992,6 +40074,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -39007,6 +40092,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -39022,6 +40110,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -39037,6 +40128,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -39052,6 +40146,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -39067,6 +40164,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -39082,6 +40182,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -39097,6 +40200,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -39112,6 +40218,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -39127,6 +40236,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -39142,6 +40254,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -39157,6 +40272,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -39172,6 +40290,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -39207,6 +40328,9 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -40367,6 +41491,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -40382,6 +41507,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -40397,6 +41523,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -40412,6 +41539,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -40427,6 +41555,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -40442,6 +41571,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -40457,6 +41587,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -40472,6 +41603,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -40487,6 +41619,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -40502,6 +41635,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -40517,6 +41651,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -40532,6 +41667,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -40547,6 +41683,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -40562,6 +41699,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -40577,6 +41715,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -40606,6 +41745,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -41436,6 +42576,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -41451,6 +42592,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -41466,6 +42608,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -41481,6 +42624,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -41496,6 +42640,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -41511,6 +42656,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -41526,6 +42672,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -41541,6 +42688,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -41556,6 +42704,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -41571,6 +42720,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -41586,6 +42736,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -41601,6 +42752,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -41616,6 +42768,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -41631,6 +42784,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -41646,6 +42800,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -41675,6 +42830,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -42119,8 +43275,12 @@
           <t>01:00</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="n">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42133,8 +43293,12 @@
           <t>02:00</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="n">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42147,8 +43311,12 @@
           <t>03:00</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="n">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42161,8 +43329,12 @@
           <t>04:00</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="n">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42175,8 +43347,12 @@
           <t>05:00</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="n">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42189,8 +43365,12 @@
           <t>06:00</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="n">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42203,8 +43383,12 @@
           <t>07:00</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="n">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42217,8 +43401,12 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="n">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42231,8 +43419,12 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="n">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42245,8 +43437,12 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="n">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42259,8 +43455,12 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="n">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42273,8 +43473,12 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="n">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42287,8 +43491,12 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="n">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42301,8 +43509,12 @@
           <t>14:00</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="n">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42315,8 +43527,12 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="n">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42329,8 +43545,12 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="n">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42343,8 +43563,12 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="n">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42357,8 +43581,12 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="n">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42371,8 +43599,12 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="n">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42385,8 +43617,12 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="n">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42399,8 +43635,12 @@
           <t>21:00</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="n">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42413,8 +43653,12 @@
           <t>22:00</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="n">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42427,8 +43671,12 @@
           <t>23:00</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="n">
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42441,8 +43689,12 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="n">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>nula_dan</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42505,6 +43757,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -42520,6 +43773,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -42535,6 +43789,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -42550,6 +43805,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -42565,6 +43821,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -42580,6 +43837,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -42595,6 +43853,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -42610,6 +43869,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -42625,6 +43885,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -42640,6 +43901,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -42655,6 +43917,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -42670,6 +43933,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -42685,6 +43949,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -42700,6 +43965,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -42715,6 +43981,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -42744,6 +44011,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -43574,6 +44842,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -43589,6 +44858,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -43604,6 +44874,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -43619,6 +44890,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -43634,6 +44906,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -43649,6 +44922,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -43664,6 +44938,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -43679,6 +44954,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -43694,6 +44970,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -43709,6 +44986,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -43724,6 +45002,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -43739,6 +45018,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -43754,6 +45034,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -43769,6 +45050,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -43784,6 +45066,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -43813,6 +45096,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -44653,6 +45937,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -44668,6 +45955,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -44683,6 +45973,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -44698,6 +45991,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -44713,6 +46009,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -44728,6 +46027,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -44743,6 +46045,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -44758,6 +46063,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -44773,6 +46081,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -44788,6 +46099,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -44803,6 +46117,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -44818,6 +46135,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -44833,6 +46153,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -44848,6 +46171,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -44863,6 +46189,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -44898,6 +46227,9 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -46068,6 +47400,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -46083,6 +47418,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -46098,6 +47436,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -46113,6 +47454,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -46128,6 +47472,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -46143,6 +47490,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -46158,6 +47508,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -46173,6 +47526,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -46188,6 +47544,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -46203,6 +47562,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -46218,6 +47580,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -46233,6 +47598,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -46248,6 +47616,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -46263,6 +47634,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -46278,6 +47652,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -46313,6 +47690,9 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -47430,7 +48810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -47554,6 +48934,66 @@
       <c r="B10" t="inlineStr">
         <is>
           <t>vrednost &gt; 400</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sivo</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>nema vrednosti za taj sat (razlog u Status)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Narandžasto: nula_dan</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>smer je ceo dan imao 0 biciklista (moguće neispravan senzor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Narandžasto: nula_niz</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>≥ 3 uzastopna sata sa 0 između 07:00 i 21:00, a smer tog dana ima ≥ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Žuto: skok</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>vrednost ≥ 50 i ≥ 3× veća od oba susedna sata</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Napomena</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>markirane vrednosti NISU menjane — markiranje samo upozorava; odluka je na korisniku</t>
         </is>
       </c>
     </row>
@@ -47611,6 +49051,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -47626,6 +49067,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -47641,6 +49083,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -47656,6 +49099,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -47671,6 +49115,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -47686,6 +49131,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -47701,6 +49147,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -47716,6 +49163,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -47731,6 +49179,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -47746,6 +49195,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -47761,6 +49211,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -47776,6 +49227,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -47791,6 +49243,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -47806,6 +49259,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -47821,6 +49275,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -47850,6 +49305,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -48680,6 +50136,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -48695,6 +50152,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -48710,6 +50168,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -48725,6 +50184,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -48740,6 +50200,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -48755,6 +50216,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -48770,6 +50232,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -48785,6 +50248,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -48800,6 +50264,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -48815,6 +50280,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -48830,6 +50296,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -48845,6 +50312,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -48860,6 +50328,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -48875,6 +50344,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -48890,6 +50360,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -48919,6 +50390,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -49749,6 +51221,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -49764,6 +51237,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -49779,6 +51253,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -49794,6 +51269,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -49809,6 +51285,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -49824,6 +51301,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -49839,6 +51317,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -49854,6 +51333,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -49869,6 +51349,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -49884,6 +51365,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -49899,6 +51381,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -49914,6 +51397,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -49929,6 +51413,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -49944,6 +51429,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -49959,6 +51445,7 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -49988,6 +51475,7 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -50828,6 +52316,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -50843,6 +52334,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -50858,6 +52352,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -50873,6 +52370,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -50888,6 +52388,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -50903,6 +52406,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -50918,6 +52424,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -50933,6 +52442,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -50948,6 +52460,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -50963,6 +52478,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -50978,6 +52496,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -50993,6 +52514,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -51008,6 +52532,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -51023,6 +52550,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -51038,6 +52568,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -51073,6 +52606,9 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -52243,6 +53779,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -52258,6 +53797,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -52273,6 +53815,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -52288,6 +53833,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -52303,6 +53851,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -52318,6 +53869,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -52333,6 +53887,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -52348,6 +53905,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -52363,6 +53923,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -52378,6 +53941,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -52393,6 +53959,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -52408,6 +53977,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -52423,6 +53995,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -52438,6 +54013,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -52453,6 +54031,9 @@
           <t>nema_citanja</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -52488,6 +54069,9 @@
           <t>nepotpun_sat</t>
         </is>
       </c>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">

--- a/podaci/excel/bicikli_2026-10.xlsx
+++ b/podaci/excel/bicikli_2026-10.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -7604,7 +7604,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -8689,7 +8689,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -14114,7 +14114,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -16296,7 +16296,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -17381,7 +17381,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -18466,7 +18466,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -19551,7 +19551,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -20636,7 +20636,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -26110,7 +26110,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -28404,7 +28404,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -29489,7 +29489,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -30574,7 +30574,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -31659,7 +31659,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -32744,7 +32744,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -33829,7 +33829,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -34914,7 +34914,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -38925,7 +38925,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -41473,7 +41473,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -42558,7 +42558,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -43739,7 +43739,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -44824,7 +44824,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -48810,7 +48810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -48844,154 +48844,166 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S&lt;n&gt; / Sum1, Sum2</t>
+          <t>y_A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>broj biciklista po smeru; Sum = zbir smerova (samo kada oba smera imaju vrednost)</t>
+          <t>broj biciklista (cilj modela) — serija sa jednim smerom</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Status prazan</t>
+          <t>Sum1, Sum2, Sum</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sat je ispravan</t>
+          <t>stari dvosmerni brojači: po smeru i zbir (Sum = y_A, samo kada oba smera imaju vrednost)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nema_citanja</t>
+          <t>Status prazan</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>čitanje u tom satu nije uspelo</t>
+          <t>sat je ispravan</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nema_smera</t>
+          <t>nema_citanja</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>u čitanju nema tog smera</t>
+          <t>čitanje u tom satu nije uspelo</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>zastarelo</t>
+          <t>nema_smera</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>podatak brojača je prestar (uređaj ne javlja nove podatke)</t>
+          <t>u čitanju nema tog smera</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>nepotpun_sat</t>
+          <t>zastarelo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>razmak čitanja nije ~1 sat</t>
+          <t>podatak brojača je prestar (uređaj ne javlja nove podatke)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>negativna_razlika</t>
+          <t>nepotpun_sat</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>brojač je resetovan</t>
+          <t>razmak čitanja nije ~1 sat</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Crveno</t>
+          <t>negativna_razlika</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>vrednost &gt; 400</t>
+          <t>brojač je resetovan</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sivo</t>
+          <t>Crveno</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nema vrednosti za taj sat (razlog u Status)</t>
+          <t>vrednost &gt; 400</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Narandžasto: nula_dan</t>
+          <t>Sivo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>smer je ceo dan imao 0 biciklista (moguće neispravan senzor)</t>
+          <t>nema vrednosti za taj sat (razlog u Status)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Narandžasto: nula_niz</t>
+          <t>Narandžasto: nula_dan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>≥ 3 uzastopna sata sa 0 između 07:00 i 21:00, a smer tog dana ima ≥ 100</t>
+          <t>smer je ceo dan imao 0 biciklista (moguće neispravan senzor)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Žuto: skok</t>
+          <t>Narandžasto: nula_niz</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>vrednost ≥ 50 i ≥ 3× veća od oba susedna sata</t>
+          <t>≥ 3 uzastopna sata sa 0 između 07:00 i 21:00, a smer tog dana ima ≥ 100</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Žuto: skok</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>vrednost ≥ 50 i ≥ 3× veća od oba susedna sata</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Napomena</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>markirane vrednosti NISU menjane — markiranje samo upozorava; odluka je na korisniku</t>
         </is>
@@ -49033,7 +49045,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -50118,7 +50130,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
@@ -51203,7 +51215,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>y_A</t>
         </is>
       </c>
     </row>
